--- a/data/trans_camb/P1412-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1412-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>-0,01</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,78</t>
+          <t>-0,8; 0,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,8</t>
+          <t>-0,71; 0,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,55</t>
+          <t>-1,23; 0,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,67</t>
+          <t>-1,08; 0,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,42</t>
+          <t>-0,74; 0,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,5</t>
+          <t>-0,57; 0,49</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,95%</t>
+          <t>-8,04%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>-0,98%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-90,03; 518,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-75,53; 471,72</t>
+          <t>-77,61; 436,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 227,21</t>
+          <t>-100,0; 204,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,93; 226,98</t>
+          <t>-68,47; 226,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,87; 147,39</t>
+          <t>-76,85; 157,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,69; 145,9</t>
+          <t>-56,25; 145,97</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,17 +764,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>-0,26</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>-0,31</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,8</t>
+          <t>-0,96; 0,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,25</t>
+          <t>-1,31; 0,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,28</t>
+          <t>-1,05; 0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,19</t>
+          <t>-0,95; 0,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,36</t>
+          <t>-0,75; 0,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,05</t>
+          <t>-0,88; 0,14</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-46,65%</t>
+          <t>-36,87%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-47,81%</t>
+          <t>-40,19%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-45,84%</t>
+          <t>-38,28%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,14; 153,58</t>
+          <t>-64,33; 206,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,61; 59,41</t>
+          <t>-79,94; 83,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 188,32</t>
+          <t>-100,0; 122,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-89,09; 91,54</t>
+          <t>-84,48; 113,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,64; 82,38</t>
+          <t>-65,69; 81,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,97; 12,41</t>
+          <t>-71,78; 37,22</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,02</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,59</t>
+          <t>-0,32; 1,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,85</t>
+          <t>-0,13; 1,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,53</t>
+          <t>-1,52; 0,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; -0,12</t>
+          <t>-1,65; -0,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,66</t>
+          <t>-0,6; 0,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,52</t>
+          <t>-0,62; 0,6</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>125,96%</t>
+          <t>121,29%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-74,24%</t>
+          <t>-63,33%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-16,34%</t>
+          <t>-2,81%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 824,16</t>
+          <t>-61,27; 821,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,95; 836,49</t>
+          <t>-40,56; 900,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,75; 129,67</t>
+          <t>-89,47; 101,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-94,32; -1,26</t>
+          <t>-89,59; 29,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,7; 131,7</t>
+          <t>-56,25; 150,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,83; 118,3</t>
+          <t>-58,1; 120,24</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,52</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,55</t>
+          <t>-0,71; 0,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,45</t>
+          <t>0,03; 1,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,04</t>
+          <t>-0,36; 0,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,76</t>
+          <t>-0,26; 0,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,59</t>
+          <t>-0,36; 0,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 0,92</t>
+          <t>0,06; 0,98</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>128,13%</t>
+          <t>134,75%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>111,95%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-82,86; 358,28</t>
+          <t>-80,76; 303,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 799,66</t>
+          <t>-17,32; 673,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,91; 678,78</t>
+          <t>-64,04; 615,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-52,93; 524,73</t>
+          <t>-38,9; 648,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 213,92</t>
+          <t>-54,89; 237,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 397,24</t>
+          <t>-0,14; 352,11</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,06</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,5</t>
+          <t>-0,32; 0,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,61</t>
+          <t>-0,15; 0,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,23</t>
+          <t>-0,54; 0,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,13</t>
+          <t>-0,51; 0,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,24</t>
+          <t>-0,32; 0,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,26</t>
+          <t>-0,2; 0,33</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-29,68%</t>
+          <t>-19,37%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-1,16%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 116,14</t>
+          <t>-37,33; 130,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 136,02</t>
+          <t>-19,31; 157,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,64; 51,07</t>
+          <t>-60,97; 45,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-61,49; 27,17</t>
+          <t>-53,77; 45,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,6; 46,1</t>
+          <t>-39,97; 42,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 51,74</t>
+          <t>-23,51; 67,19</t>
         </is>
       </c>
     </row>
